--- a/outputs/operacional/auditoria/Status_vs_Situacao.xlsx
+++ b/outputs/operacional/auditoria/Status_vs_Situacao.xlsx
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>53.8</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="b">
         <v>1</v>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.9</v>
+        <v>45.7</v>
       </c>
       <c r="E3" s="3" t="b">
         <v>0</v>
@@ -6926,7 +6926,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="F212" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="F213" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">

--- a/outputs/operacional/auditoria/Status_vs_Situacao.xlsx
+++ b/outputs/operacional/auditoria/Status_vs_Situacao.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_Agregado'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_Lastro'!$A$1:$F$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_Lastro'!$A$1:$F$247</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>53</v>
+        <v>53.7</v>
       </c>
       <c r="E2" s="2" t="b">
         <v>1</v>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="E3" s="3" t="b">
         <v>0</v>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E4" s="2" t="b">
         <v>0</v>
@@ -580,14 +580,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F248"/>
+  <dimension ref="A1:F247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -636,12 +636,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>02278469973</t>
+          <t>01372151070</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>02771670145</t>
+          <t>01372151070</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>PRODUTO TESTE NAO MAPEADO</t>
         </is>
       </c>
       <c r="F3" s="3" t="b">
@@ -686,7 +686,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -696,27 +696,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>02786814473</t>
+          <t>01398373540</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>02786814473</t>
+          <t>01581449147</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="F5" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -756,12 +756,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>03070534578</t>
+          <t>01676184723</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -786,21 +786,21 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>03669096705</t>
+          <t>02278469973</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F7" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -816,17 +816,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>04091570184</t>
+          <t>02726149331</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F8" s="2" t="b">
@@ -846,17 +846,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>04633312797</t>
+          <t>02843959953</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F9" s="3" t="b">
@@ -876,7 +876,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>04633312797</t>
+          <t>03669096705</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F10" s="2" t="b">
@@ -896,7 +896,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>04727790104</t>
+          <t>04091570184</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -936,17 +936,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>04899642353</t>
+          <t>04341651827</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F12" s="2" t="b">
@@ -956,7 +956,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>04899642353</t>
+          <t>04341651827</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -996,27 +996,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>05129276637</t>
+          <t>04556110022</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F14" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1026,21 +1026,21 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>05415667652</t>
+          <t>04556110022</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F15" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>05891135290</t>
+          <t>06181753443</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>05891135290</t>
+          <t>06356512694</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F17" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>06706540515</t>
+          <t>06356512694</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="F18" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1146,27 +1146,27 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>07432927129</t>
+          <t>06724004991</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F19" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1176,27 +1176,27 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>07903067383</t>
+          <t>06724004991</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F20" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1206,27 +1206,27 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>08240433504</t>
+          <t>07596599920</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1236,21 +1236,21 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>08240433504</t>
+          <t>07596599920</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F23" s="3" t="b">
@@ -1286,7 +1286,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1296,21 +1296,21 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>08740640391</t>
+          <t>08613171274</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>08740640391</t>
+          <t>08635365419</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>09435334485</t>
+          <t>08993588916</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F27" s="3" t="b">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>09805009788</t>
+          <t>09859317461</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F28" s="2" t="b">
@@ -1436,7 +1436,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1446,21 +1446,21 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>10433218196</t>
+          <t>11266912153</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F29" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>11266912153</t>
+          <t>11435190669</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F30" s="2" t="b">
@@ -1496,7 +1496,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1506,27 +1506,27 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>11266912153</t>
+          <t>12499856984</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F31" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1536,27 +1536,27 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>11908334280</t>
+          <t>12499856984</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F32" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>12499856984</t>
+          <t>13433200379</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F33" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>12679692786</t>
+          <t>13736785082</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>13433200379</t>
+          <t>13875927125</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>13836702410</t>
+          <t>14429444019</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F36" s="2" t="b">
@@ -1686,17 +1686,17 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>13858542493</t>
+          <t>14921643347</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F37" s="3" t="b">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>13858542493</t>
+          <t>15313636317</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>13875927125</t>
+          <t>15451680876</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F39" s="3" t="b">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>13875927125</t>
+          <t>17187026217</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1806,27 +1806,27 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>14163356588</t>
+          <t>17535560932</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F41" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1836,21 +1836,21 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>14590099217</t>
+          <t>18102203173</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F42" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1866,17 +1866,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>15274205493</t>
+          <t>18785191088</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F43" s="3" t="b">
@@ -1886,7 +1886,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1896,21 +1896,21 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>15313636317</t>
+          <t>18785191088</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F44" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1926,17 +1926,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>15890429025</t>
+          <t>18835523124</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F45" s="3" t="b">
@@ -1946,7 +1946,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>16400524278</t>
+          <t>18835523124</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F46" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1986,21 +1986,21 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>17187026217</t>
+          <t>19906234456</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F47" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>17839084700</t>
+          <t>20417929111</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>17839084700</t>
+          <t>20417929111</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F49" s="3" t="b">
@@ -2066,7 +2066,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2076,21 +2076,21 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>17839084700</t>
+          <t>20417929111</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F50" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>18233984546</t>
+          <t>20616329451</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2126,7 +2126,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2136,21 +2136,21 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>18449892665</t>
+          <t>20616329451</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F52" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>19148564679</t>
+          <t>20616329451</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F53" s="3" t="b">
@@ -2186,7 +2186,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2196,27 +2196,27 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>19148564679</t>
+          <t>20812191361</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F54" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2226,27 +2226,27 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>19656523413</t>
+          <t>22499982795</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F55" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2256,21 +2256,21 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>19906234456</t>
+          <t>22499982795</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F56" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2286,17 +2286,17 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>19906234456</t>
+          <t>22535841438</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F57" s="3" t="b">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>20644742123</t>
+          <t>22820055778</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F58" s="2" t="b">
@@ -2336,7 +2336,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2346,27 +2346,27 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>20644742123</t>
+          <t>22901476797</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F59" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2376,21 +2376,21 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>20812191361</t>
+          <t>23884969653</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F60" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>21495870207</t>
+          <t>24451076226</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -2426,7 +2426,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2436,21 +2436,21 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>22656766182</t>
+          <t>24508821009</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F62" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>22901476797</t>
+          <t>24508821009</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F63" s="3" t="b">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>22961201836</t>
+          <t>24593344196</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2526,27 +2526,27 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>24051477053</t>
+          <t>25546659051</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F65" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2556,21 +2556,21 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>24056829962</t>
+          <t>26368970283</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F66" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>25381793355</t>
+          <t>26368970283</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F67" s="3" t="b">
@@ -2606,7 +2606,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2616,21 +2616,21 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>25462914865</t>
+          <t>26984858333</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F68" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>25534192832</t>
+          <t>26984858333</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F69" s="3" t="b">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>25699611253</t>
+          <t>27238046827</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>26011939103</t>
+          <t>27570596401</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="F71" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>26011939103</t>
+          <t>28168505423</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2766,27 +2766,27 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>26204505331</t>
+          <t>28168505423</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F73" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>CANCELADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2796,21 +2796,21 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>26860259222</t>
+          <t>28685289755</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F74" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>27111161528</t>
+          <t>29218515691</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F75" s="3" t="b">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>27128639174</t>
+          <t>30385677005</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2886,21 +2886,21 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>27128639174</t>
+          <t>31752071678</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F77" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>27238046827</t>
+          <t>31952058527</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F78" s="2" t="b">
@@ -2936,7 +2936,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2946,21 +2946,21 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>28685289755</t>
+          <t>32677360260</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F79" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2976,17 +2976,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>28699041379</t>
+          <t>32898614341</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F80" s="2" t="b">
@@ -2996,7 +2996,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3006,27 +3006,27 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>28699041379</t>
+          <t>33173936385</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F81" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>32161107603</t>
+          <t>33173936385</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="F82" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>32898614341</t>
+          <t>35031365024</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F83" s="3" t="b">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>33898881671</t>
+          <t>36403761379</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F84" s="2" t="b">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>34125286692</t>
+          <t>36815798123</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3156,21 +3156,21 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>34163894484</t>
+          <t>37124065965</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F86" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>34721228160</t>
+          <t>37562890028</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>35158807053</t>
+          <t>37562890028</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F88" s="2" t="b">
@@ -3246,17 +3246,17 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>35290422842</t>
+          <t>37562890028</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F89" s="3" t="b">
@@ -3266,7 +3266,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>35569092755</t>
+          <t>37693898331</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3290,13 +3290,13 @@
         </is>
       </c>
       <c r="F90" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3306,27 +3306,27 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>36403761379</t>
+          <t>37693898331</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F91" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -3336,21 +3336,21 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>36403761379</t>
+          <t>37923747407</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F92" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>37562890028</t>
+          <t>37996507527</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>37923747407</t>
+          <t>38657191826</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F94" s="2" t="b">
@@ -3416,7 +3416,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3426,27 +3426,27 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>37923747407</t>
+          <t>38663177971</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F95" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>38657191826</t>
+          <t>39382761539</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="F96" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3486,27 +3486,27 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>38663177971</t>
+          <t>39382761539</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F97" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3516,27 +3516,27 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>38663177971</t>
+          <t>39385258001</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F98" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>39103717058</t>
+          <t>39690784473</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3576,27 +3576,27 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>39660558303</t>
+          <t>40321153550</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F100" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>39690784473</t>
+          <t>42498182992</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3620,13 +3620,13 @@
         </is>
       </c>
       <c r="F101" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>39878015739</t>
+          <t>42579913662</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>40084271094</t>
+          <t>42701039308</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>40640909743</t>
+          <t>42843479552</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F104" s="2" t="b">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>41395376724</t>
+          <t>42843479552</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F105" s="3" t="b">
@@ -3746,7 +3746,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -3756,21 +3756,21 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>42622189092</t>
+          <t>44270312073</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F106" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>42625827390</t>
+          <t>44714627301</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
@@ -3816,17 +3816,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>42626551104</t>
+          <t>45868501429</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F108" s="2" t="b">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>42626551104</t>
+          <t>45868501429</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F109" s="3" t="b">
@@ -3866,7 +3866,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -3876,27 +3876,27 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>42836440892</t>
+          <t>46591166553</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F110" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3906,27 +3906,27 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>42843479552</t>
+          <t>46591166553</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F111" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>43280634615</t>
+          <t>46785445877</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -3946,11 +3946,11 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F112" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>43757584419</t>
+          <t>47284639208</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F113" s="3" t="b">
@@ -3986,7 +3986,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -3996,21 +3996,21 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>43805719838</t>
+          <t>47411249035</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F114" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -4026,17 +4026,17 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>44144885015</t>
+          <t>48640155778</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F115" s="3" t="b">
@@ -4046,7 +4046,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -4056,27 +4056,27 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>44144885015</t>
+          <t>49588039551</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F116" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>CANCELADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>44270312073</t>
+          <t>49947174648</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -4100,13 +4100,13 @@
         </is>
       </c>
       <c r="F117" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>44935348740</t>
+          <t>49947174648</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>45547813767</t>
+          <t>49972787558</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -4176,27 +4176,27 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>45547813767</t>
+          <t>50375899757</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F120" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>45868501429</t>
+          <t>50375899757</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F121" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -4236,27 +4236,27 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>46187234601</t>
+          <t>51256746807</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F122" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4266,21 +4266,21 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>46287334270</t>
+          <t>51432191430</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F123" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -4296,17 +4296,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>46287334270</t>
+          <t>51583281826</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F124" s="2" t="b">
@@ -4316,7 +4316,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>46688937346</t>
+          <t>51583281826</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F125" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>47132475469</t>
+          <t>51820377889</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>47284639208</t>
+          <t>52677223306</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F127" s="3" t="b">
@@ -4406,7 +4406,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -4416,21 +4416,21 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>47284639208</t>
+          <t>54019380262</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F128" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>47859696915</t>
+          <t>54451895202</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -4466,7 +4466,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -4476,27 +4476,27 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>48640155778</t>
+          <t>54522675289</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F130" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4506,21 +4506,21 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>48728299796</t>
+          <t>54788728743</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F131" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>48728299796</t>
+          <t>54788728743</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F132" s="2" t="b">
@@ -4556,7 +4556,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4566,21 +4566,21 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>49588039551</t>
+          <t>55449647598</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F133" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>49947174648</t>
+          <t>55460158517</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>49947174648</t>
+          <t>55794155216</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="F135" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>50375899757</t>
+          <t>56083318195</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F136" s="2" t="b">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>50375899757</t>
+          <t>56083318195</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F137" s="3" t="b">
@@ -4706,7 +4706,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -4716,27 +4716,27 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>50613878293</t>
+          <t>56342160733</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F138" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4746,27 +4746,27 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>50648909010</t>
+          <t>56475705120</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F139" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>50648909010</t>
+          <t>56475705120</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F140" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4806,27 +4806,27 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>51509398343</t>
+          <t>57437489691</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F141" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -4836,27 +4836,27 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>51713395962</t>
+          <t>57437489691</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F142" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4866,21 +4866,21 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>51713395962</t>
+          <t>57662702895</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F143" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>51939828073</t>
+          <t>57905528183</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F144" s="2" t="b">
@@ -4916,7 +4916,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4926,27 +4926,27 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>52056647423</t>
+          <t>57905528183</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F145" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>52064361103</t>
+          <t>58514936899</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="F146" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4986,21 +4986,21 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>52677223306</t>
+          <t>58842524105</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F147" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>53926442209</t>
+          <t>59255562588</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F148" s="2" t="b">
@@ -5036,7 +5036,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5046,27 +5046,27 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>53926442209</t>
+          <t>59831244129</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F149" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>CANCELADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -5076,21 +5076,21 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>54353462475</t>
+          <t>59916247314</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F150" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>54451895202</t>
+          <t>60466183982</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F151" s="3" t="b">
@@ -5126,7 +5126,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>54451895202</t>
+          <t>60843256216</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F152" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5166,21 +5166,21 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>54522675289</t>
+          <t>61581487696</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F153" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>54544432830</t>
+          <t>61847870050</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F154" s="2" t="b">
@@ -5216,7 +5216,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5226,27 +5226,27 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>54788728743</t>
+          <t>62713611155</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F155" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>54868740345</t>
+          <t>62713611155</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="F156" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5286,27 +5286,27 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>54868740345</t>
+          <t>63122417974</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F157" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -5316,21 +5316,21 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>55231491357</t>
+          <t>63745458929</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F158" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>55394237333</t>
+          <t>63840666580</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F159" s="3" t="b">
@@ -5376,17 +5376,17 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>56083318195</t>
+          <t>64710276773</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F160" s="2" t="b">
@@ -5396,7 +5396,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5406,21 +5406,21 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>56704310385</t>
+          <t>64746872343</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F161" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>56704310385</t>
+          <t>64842294057</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F162" s="2" t="b">
@@ -5456,7 +5456,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5466,21 +5466,21 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>57027937145</t>
+          <t>65094801413</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F163" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>57332214188</t>
+          <t>65766156545</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -5526,17 +5526,17 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>57332214188</t>
+          <t>66383615171</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F165" s="3" t="b">
@@ -5546,7 +5546,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -5556,21 +5556,21 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>57366096569</t>
+          <t>66978480184</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F166" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -5586,17 +5586,17 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>57662702895</t>
+          <t>66978480184</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F167" s="3" t="b">
@@ -5606,7 +5606,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -5616,21 +5616,21 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>57924991251</t>
+          <t>67808562718</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F168" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -5646,17 +5646,17 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>58514936899</t>
+          <t>67883171210</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F169" s="3" t="b">
@@ -5666,7 +5666,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>59059929378</t>
+          <t>67883171210</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -5686,17 +5686,17 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F170" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>59059929378</t>
+          <t>68414593327</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="F171" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>59916247314</t>
+          <t>68486661889</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5766,21 +5766,21 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>59916247314</t>
+          <t>68486661889</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F173" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -5796,17 +5796,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>61595148465</t>
+          <t>69340608835</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F174" s="2" t="b">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>62003424420</t>
+          <t>69804204394</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F175" s="3" t="b">
@@ -5846,7 +5846,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -5856,21 +5856,21 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>62003424420</t>
+          <t>69804204394</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F176" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>62244472126</t>
+          <t>70805310033</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -5916,17 +5916,17 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>63122417974</t>
+          <t>70805310033</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F178" s="2" t="b">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>63942788165</t>
+          <t>71236851604</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -5976,27 +5976,27 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>63942788165</t>
+          <t>71236851604</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F180" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>64240082547</t>
+          <t>71422410988</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F181" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>64710276773</t>
+          <t>71422410988</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F182" s="2" t="b">
@@ -6056,7 +6056,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6066,27 +6066,27 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>64746872343</t>
+          <t>71732030937</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F183" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -6096,21 +6096,21 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>64794738646</t>
+          <t>71902294131</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F184" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -6126,17 +6126,17 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>64794738646</t>
+          <t>74034471349</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F185" s="3" t="b">
@@ -6146,7 +6146,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -6156,27 +6156,27 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>65307450544</t>
+          <t>74993097289</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F186" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6186,27 +6186,27 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>65375564641</t>
+          <t>74993097289</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F187" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -6216,21 +6216,21 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>65375564641</t>
+          <t>75304637454</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F188" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -6246,17 +6246,17 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>68011280598</t>
+          <t>75304637454</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F189" s="3" t="b">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>68486661889</t>
+          <t>75326973112</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F190" s="2" t="b">
@@ -6296,7 +6296,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6306,21 +6306,21 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>68793741608</t>
+          <t>75869261796</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F191" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>69308488725</t>
+          <t>76973577907</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F192" s="2" t="b">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>69378547772</t>
+          <t>76973577907</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F193" s="3" t="b">
@@ -6396,17 +6396,17 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>69378547772</t>
+          <t>77418625652</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F194" s="2" t="b">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>70335211039</t>
+          <t>77547812914</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F195" s="3" t="b">
@@ -6456,17 +6456,17 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>71434558122</t>
+          <t>77584161692</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F196" s="2" t="b">
@@ -6476,7 +6476,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>71657262849</t>
+          <t>77584161692</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="F197" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>74783667428</t>
+          <t>77739260302</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F198" s="2" t="b">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>75003691559</t>
+          <t>78078235784</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>75304637454</t>
+          <t>78161849593</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="F200" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -6606,17 +6606,17 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>75901751863</t>
+          <t>78232983248</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F201" s="3" t="b">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>76365564729</t>
+          <t>78291146786</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F202" s="2" t="b">
@@ -6666,17 +6666,17 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>76617711592</t>
+          <t>79827080869</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F203" s="3" t="b">
@@ -6686,7 +6686,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -6696,21 +6696,21 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>76617711592</t>
+          <t>79968460810</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="F204" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -6726,17 +6726,17 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>77418625652</t>
+          <t>80841241182</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F205" s="3" t="b">
@@ -6746,7 +6746,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -6756,21 +6756,21 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>77418625652</t>
+          <t>80940244550</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F206" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>77739260302</t>
+          <t>81273585730</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -6816,27 +6816,27 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>78292216995</t>
+          <t>81273585730</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F208" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6846,27 +6846,27 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>78774701687</t>
+          <t>81845184894</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F209" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -6876,21 +6876,21 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>80392827229</t>
+          <t>83388487920</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F210" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -6906,17 +6906,17 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>80841241182</t>
+          <t>83473597746</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F211" s="3" t="b">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>80940244550</t>
+          <t>84902770384</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>81273585730</t>
+          <t>84902770384</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
@@ -6986,7 +6986,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -6996,21 +6996,21 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>81814124782</t>
+          <t>85524140602</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F214" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>81845184894</t>
+          <t>86101581995</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -7056,17 +7056,17 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>82586736226</t>
+          <t>86652404157</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F216" s="2" t="b">
@@ -7086,17 +7086,17 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>82586736226</t>
+          <t>86693465472</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F217" s="3" t="b">
@@ -7116,17 +7116,17 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>82974255136</t>
+          <t>87258874495</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F218" s="2" t="b">
@@ -7146,17 +7146,17 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>83473597746</t>
+          <t>87653269097</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F219" s="3" t="b">
@@ -7166,7 +7166,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -7176,21 +7176,21 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>84511544796</t>
+          <t>87719065940</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F220" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -7206,17 +7206,17 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>85368663266</t>
+          <t>87719065940</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F221" s="3" t="b">
@@ -7226,7 +7226,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -7236,27 +7236,27 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>85368663266</t>
+          <t>88608680347</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F222" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7266,21 +7266,21 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>85474929751</t>
+          <t>88615335554</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F223" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>85642059304</t>
+          <t>88615335554</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F224" s="2" t="b">
@@ -7316,7 +7316,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7326,27 +7326,27 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>85681193978</t>
+          <t>89137189490</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F225" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -7356,21 +7356,21 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>86753396360</t>
+          <t>89994043898</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F226" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -7386,17 +7386,17 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>86753396360</t>
+          <t>89994043898</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F227" s="3" t="b">
@@ -7416,17 +7416,17 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>87258874495</t>
+          <t>90340438427</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F228" s="2" t="b">
@@ -7436,7 +7436,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>89026012796</t>
+          <t>91630097925</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -7456,11 +7456,11 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F229" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>89994043898</t>
+          <t>91846386557</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7506,27 +7506,27 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>89994043898</t>
+          <t>92750373145</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F231" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -7536,17 +7536,17 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>90604805892</t>
+          <t>93157279194</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F232" s="2" t="b">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>91463031617</t>
+          <t>93305172897</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F233" s="3" t="b">
@@ -7596,17 +7596,17 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>93305172897</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F234" s="2" t="b">
@@ -7626,17 +7626,17 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>93333468007</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F235" s="3" t="b">
@@ -7646,7 +7646,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -7656,27 +7656,27 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>91965701329</t>
+          <t>93990916998</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F236" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>95701543039</t>
+          <t>96499091334</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="F237" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>95701543039</t>
+          <t>96561014388</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F238" s="2" t="b">
@@ -7736,7 +7736,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>95701543039</t>
+          <t>96561014388</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -7756,11 +7756,11 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="F239" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>96520744666</t>
+          <t>96631931491</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7806,21 +7806,21 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>96520744666</t>
+          <t>96631931491</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F241" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -7836,17 +7836,17 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>96627828274</t>
+          <t>96881435368</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F242" s="2" t="b">
@@ -7866,17 +7866,17 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>98253092511</t>
+          <t>96881435368</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="F243" s="3" t="b">
@@ -7886,7 +7886,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -7896,21 +7896,21 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>98253092511</t>
+          <t>97252175250</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="F244" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -7926,17 +7926,17 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>98616229991</t>
+          <t>98992172233</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F245" s="3" t="b">
@@ -7946,7 +7946,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>INATIVO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -7956,27 +7956,27 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>99758172461</t>
+          <t>99042102027</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="F246" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>INATIVO</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7986,55 +7986,25 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>99880817703</t>
+          <t>99552717744</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="F247" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>Ativa</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>99880817703</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>DELT</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr">
-        <is>
-          <t>RESIDENCIAL</t>
-        </is>
-      </c>
-      <c r="F248" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F248"/>
+  <autoFilter ref="A1:F247"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>